--- a/mosques/المساجد المتجاوزة في الربع الأول لعام 2025- موزعة حسب الجهات.xlsx
+++ b/mosques/المساجد المتجاوزة في الربع الأول لعام 2025- موزعة حسب الجهات.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mpet-my.sharepoint.com/personal/alosaink_mopm_gov_sa/Documents/Documents/dashboard v2/latest ver/mosques-dashboard.v2/mosques/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mpet-my.sharepoint.com/personal/alosaink_mopm_gov_sa/Documents/Documents/Mosques/mosques-dashboard-v2/mosques/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_97650A953ABD3C007C8414860ED8FB94C7D828C3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0BF9983-26C1-4E1D-8879-787FDA7CE040}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_97650A953ABD3C007C8414860ED8FB94C7D828C3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE57D2F4-DEC0-4B4A-8C1B-D51225C2378D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61362,7 +61362,8 @@
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="99" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
